--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-organization.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T12:29:31+00:00</t>
+    <t>2023-06-02T14:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -354,7 +354,7 @@
     <t>as-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-data-trace}
 </t>
   </si>
   <si>
@@ -760,7 +760,7 @@
     <t>as-ext-digital-certificate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate}
 </t>
   </si>
   <si>
@@ -779,7 +779,7 @@
     <t>as-ext-organization-pharmacy-licence</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-organization-pharmacy-licence}
 </t>
   </si>
   <si>
@@ -1552,7 +1552,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended}
+    <t xml:space="preserve">Address {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-address-extended}
 </t>
   </si>
   <si>
@@ -1575,7 +1575,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
+    <t xml:space="preserve">Reference(http://interopsante.org/fhir/StructureDefinition/FrOrganization|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization)
 </t>
   </si>
   <si>
@@ -1773,7 +1773,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss}
 </t>
   </si>
   <si>
@@ -1798,7 +1798,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata}
 </t>
   </si>
   <si>
@@ -2027,7 +2027,7 @@
     <t>Organization.contact.telecom.extension.url</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.value[x]</t>

--- a/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T14:39:58+00:00</t>
+    <t>2023-06-02T15:19:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
